--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
@@ -1348,20 +1348,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Software Development Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Sr. Engineer - Software Development Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer Advanced</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cbdb0aac5bd79a</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,42 +2246,427 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Software Development Engineer Advanced</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, MySQL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18cbdb0aac5bd79a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer- People Analytics</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ARS/Rescue Rooter</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>University of California - San Francisco</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Tessera Labs</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>San Jose, CA, US USA</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D61" t="n">
         <v>10.4</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Software Development Engineering</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,164 +1861,164 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer Advanced</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, MySQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cbdb0aac5bd79a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,15 +2656,225 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>University of California - San Francisco</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,38 +1042,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,15 +2866,155 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Ziply Fiber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>31.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a6405304b5156b40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b55a7fd76f93036a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,64 +1046,64 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,38 +1112,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,104 +1991,104 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,77 +2096,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,15 +3006,85 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,120 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,104 +2061,104 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Oracle, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,69 +2306,69 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,50 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,69 +2341,69 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55a7fd76f93036a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,139 +2026,139 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,137 +2211,137 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3155,111 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,104 +1956,104 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>US LBM Domain Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3050,111 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,25 +1378,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,104 +1886,104 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>SR Data Scientist, Rental</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US LBM Domain Data Architect</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8285c6efc2fd5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,76 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,139 +1781,139 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer - DBT &amp; Redshift</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR Data Scientist, Rental</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SR Data Scientist, Rental</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2840,146 +2840,6 @@
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,64 +731,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e861a98af18e6eab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433363ccf862c4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949bdab6f7ff4504</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) with a Performance Focus</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,69 +1746,69 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78c7be20b2c19df</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,112 +1921,112 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DBT &amp; Redshift</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Medallion Architecture, Scala, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35214e13f0757c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SR Data Scientist, Rental</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>SR Data Scientist, Rental</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software and DevOps Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
@@ -1413,25 +1413,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1973,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SR Data Scientist, Rental</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>SR Data Scientist, Rental</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,15 +2831,85 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,99 +766,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,38 +867,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,29 +1221,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>BI / Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,207 +1686,207 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,242 +1896,242 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,164 +2246,164 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SR Data Scientist, Rental</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,52 +2446,52 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
@@ -2503,20 +2503,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Engineer III, Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,54 +2806,54 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,15 +2901,365 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer- People Analytics</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>University of California - San Francisco</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e4f57f20c8e6aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>BI / Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,52 +1886,52 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a53ba237c911865</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,94 +2281,94 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- People Analytics</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
+          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Engineer III, Business Intelligence</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,41 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e4f57f20c8e6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,54 +1091,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,46 +1147,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Sr Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,38 +1392,38 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>BI / Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a53ba237c911865</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,119 +1931,119 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,85 +2053,85 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer III, Software</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae1f80649c49a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Information Security- Assoc Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,129 +3086,129 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,435 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INFINITY HOME SERVICES</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Jean Martin</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>University of California - San Francisco</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Accelerate Learning Inc.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Engineer III, Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mobis Parts America, LLC.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fountain Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>SAP Datasphere Integration Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
@@ -1728,25 +1728,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FloQast</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Cards Java Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,42 +2666,42 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BAKER GROUP</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (Basketball Operations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New Orleans Saints and Pelicans</t>
+          <t>BAKER GROUP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5b98e60496f48</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Information Security- Assoc Specialist</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb0c102170c1a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Accelerate Learning Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer III, Business Intelligence</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Sr. Network Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Accelerate Learning Inc.</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,85 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Engineer III, Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Mobis Parts America, LLC.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Fountain Valley, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Network Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
         </is>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,54 +1231,54 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAP Datasphere Integration Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,38 +1287,38 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf7ef025c86465d</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Bioinformatics Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>UNISON Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3bf0e2cbc7964d</t>
+          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>REV LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,38 +2862,38 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer (175364)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee3bf5d93813275</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
         </is>
       </c>
     </row>
@@ -3273,90 +3273,90 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,94 +3366,94 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Accelerate Learning Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,297 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2d6b8d6e19c920</t>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>University of California - San Francisco</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Accelerate Learning Inc.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Engineer III, Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mobis Parts America, LLC.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fountain Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-25.xlsx
+++ b/results/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=181a31f219accf44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=493f15e83d88a6ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>AWS Python Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,29 +941,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=834d52dff47fe0c1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Peoples Gas System</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, Cloud Storage, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3035f2b8b17e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Senior Systems Engineer, Data Management</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Java Developer | Jersey City, US</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, BigQuery</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Backend Java Developer | Jersey City, US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3331c9e1ce571b88</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791da096375caa98</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UNISON Group</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755ae6e158f294ba</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, SQS, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b42ed4ff39a3e5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>BI / Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer | Wilmington/New York, US</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)</t>
+          <t>Full Stack Engineer | New York, US</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64614fd6a49cf213</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,29 +1641,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,73 +1672,73 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Spark, Scala, Oracle, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=2784516465b56a61</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Vertex AI, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,172 +1896,172 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Wrench.ai Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=83be4ed684048bae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4cf4f64edea884</t>
+          <t>https://www.indeed.com/viewjob?jk=2932f50360d701f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679d5d1c7a09b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45ff3218e58d2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Whiteland, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd72ec86ae1741</t>
+          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Whiteland, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895b46639975055d</t>
+          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant - Sn. DevSecOps Engineer</t>
+          <t>Cards Java Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e23617f258b60</t>
+          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cards Java Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Praia Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5208fb6417aa24f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Praia Health</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD</t>
+          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66607f3c1e40fc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Sr. Data Engineer with Azure Databricks</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aurum Groups</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Innovation Delivery Platform Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer with Azure Databricks</t>
+          <t>Data Platform &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aurum Groups</t>
+          <t>Gopher Resource, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f335aa71e7b3af</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL Database Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>BMR infotek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gopher Resource, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbe8604e2f80090</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=95a325a771df03df</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, DynamoDB, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Database Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BMR infotek</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0cc3caaa083f92</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>REV LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,42 +2796,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, GCP, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c4b5ed942f8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,42 +2841,42 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1c0dc02d7f1f51</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe189c15997f93c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=d358ff0176b96002</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bd60899be1448</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc529933e7d8181d</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, MLflow, Docker, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate - NASA</t>
+          <t>Controller Transformation Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, CI/CD, Docker, Kubernetes, Bitbucket</t>
+          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
+          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Controller Transformation Analyst</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling, ETL, ELT, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72f210004930cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>INFINITY HOME SERVICES</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Jean Martin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jean Martin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc27939551ef0306</t>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,29 +3671,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18271f0af24fff11</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Accelerate Learning Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, Business Intelligence</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,120 +3741,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbb0f0c71cc7c53</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Accelerate Learning Inc.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddf4a6188d3a180</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Engineer III, Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Mobis Parts America, LLC.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Fountain Valley, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b3103a10d60cdc6</t>
         </is>
